--- a/File_1_Storage_space_application_form.xlsx
+++ b/File_1_Storage_space_application_form.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Storage space application form</t>
   </si>
@@ -50,7 +50,13 @@
     <t>100 GB</t>
   </si>
   <si>
-    <t>Send this file to chenhaojie2017@sinh.ac.cn</t>
+    <t>sign the User Service and Data Use Agreement</t>
+  </si>
+  <si>
+    <t>https://github.com/haojiechen94/EAP/blob/main/doc/EAP%E5%B9%B3%E5%8F%B0%E7%94%A8%E6%88%B7%E6%9C%8D%E5%8A%A1%E4%B8%8E%E6%95%B0%E6%8D%AE%E4%BD%BF%E7%94%A8%E5%8D%8F%E8%AE%AE_EAP%20Platform%20User%20Service%20and%20Data%20Use%20Agreement.docx</t>
+  </si>
+  <si>
+    <t>Send these file to chenhaojie2017@sinh.ac.cn</t>
   </si>
 </sst>
 </file>
@@ -92,19 +98,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -581,7 +587,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -711,7 +717,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -727,7 +733,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1049,8 +1058,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="45.8" style="1" customWidth="1"/>
     <col min="2" max="2" width="49.8636363636364" style="1" customWidth="1"/>
@@ -1058,7 +1067,7 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:1">
+    <row r="1" ht="20" customHeight="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1087,12 +1096,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
+    <row r="5" ht="105" customHeight="1" spans="1:2">
+      <c r="A5" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" display="https://github.com/haojiechen94/EAP/blob/main/doc/EAP%E5%B9%B3%E5%8F%B0%E7%94%A8%E6%88%B7%E6%9C%8D%E5%8A%A1%E4%B8%8E%E6%95%B0%E6%8D%AE%E4%BD%BF%E7%94%A8%E5%8D%8F%E8%AE%AE_EAP%20Platform%20User%20Service%20and%20Data%20Use%20Agreement.docx"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
